--- a/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2607" uniqueCount="549">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,16 +656,6 @@
     <t>檢驗檢查分類</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Observation.category:VSCat.id</t>
   </si>
   <si>
@@ -938,6 +928,24 @@
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/vital-signs-tw</t>
   </si>
   <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
+  </si>
+  <si>
     <t>Observation.code.id</t>
   </si>
   <si>
@@ -969,12 +977,6 @@
     <t>允許代碼系統中的替代編碼，以及翻譯到其他編碼系統。</t>
   </si>
   <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
-  </si>
-  <si>
     <t>Observation.code.text</t>
   </si>
   <si>
@@ -1012,7 +1014,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1023,9 +1025,6 @@
   </si>
   <si>
     <t>通常檢驗檢查的對象是一位病人或一群病人、地點或設備，檢驗檢查對象與直接測量內容之間的區別在observation.code已具體說明（例如： 「血糖」），不需要使用這個資料項目（focus）單獨表示。如果需要參照檢體，則使用specimen，如果需要一個代碼而不是一個resource，則使用bodysite來表示bodysites或標準擴充focusCode。</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1225,6 +1224,13 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
+    <t>obs-6
+vs-2</t>
+  </si>
+  <si>
+    <t>value.nullFlavor</t>
+  </si>
+  <si>
     <t>Observation.interpretation</t>
   </si>
   <si>
@@ -1250,6 +1256,18 @@
     <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
+    <t>&lt; 260245000 |Findings values|</t>
+  </si>
+  <si>
+    <t>OBX-8</t>
+  </si>
+  <si>
+    <t>interpretationCode</t>
+  </si>
+  <si>
+    <t>363713009 |Has interpretation|</t>
+  </si>
+  <si>
     <t>Observation.note</t>
   </si>
   <si>
@@ -1294,6 +1312,18 @@
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
+    <t>&lt; 123037004 |Body structure|</t>
+  </si>
+  <si>
+    <t>OBX-20</t>
+  </si>
+  <si>
+    <t>targetSiteCode</t>
+  </si>
+  <si>
+    <t>718497002 |Inherent location|</t>
+  </si>
+  <si>
     <t>Observation.method</t>
   </si>
   <si>
@@ -1313,6 +1343,12 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+  </si>
+  <si>
+    <t>OBX-17</t>
+  </si>
+  <si>
+    <t>methodCode</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -1347,7 +1383,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1428,7 +1464,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1478,6 +1514,18 @@
     <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
+    <t>&lt; 260245000 |Findings values| OR  +&lt; 365860008 |General clinical state finding| +OR +&lt; 250171008 |Clinical history or observation findings| OR  +&lt; 415229000 |Racial group| OR +&lt; 365400002 |Finding of puberty stage| OR+&lt; 443938003 |Procedure carried out on subject|</t>
+  </si>
+  <si>
+    <t>OBX-10</t>
+  </si>
+  <si>
     <t>Observation.referenceRange.appliesTo</t>
   </si>
   <si>
@@ -1620,6 +1668,10 @@
     <t>代碼指明檢驗檢查的名稱；可參考所綁定值集，但此值集只是針對這個欄位的一個可能值的範例，不預期也不鼓勵使用者一定要使用此值集的代碼。</t>
   </si>
   <si>
+    <t>&lt; 363787002 |Observable entity| OR +&lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
     <t>Observation.component.value[x]</t>
   </si>
   <si>
@@ -1658,6 +1710,10 @@
   </si>
   <si>
     <t>代碼指明為什麼結果（Observation.value[x]）缺少；應填入所綁定值集中適合的代碼，確定無適合的代碼才可以使用其他值集的代碼來表示。</t>
+  </si>
+  <si>
+    <t>obs-6
+vs-3</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2031,7 +2087,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="46.26953125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -3948,7 +4004,7 @@
         <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>104</v>
@@ -3960,13 +4016,13 @@
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>20</v>
@@ -3974,10 +4030,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4000,13 +4056,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4057,7 +4113,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4081,7 +4137,7 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4092,10 +4148,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4124,7 +4180,7 @@
         <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>142</v>
@@ -4165,10 +4221,10 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
@@ -4177,7 +4233,7 @@
         <v>199</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4201,7 +4257,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4212,10 +4268,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4238,19 +4294,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4299,7 +4355,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4320,10 +4376,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -4334,10 +4390,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4360,13 +4416,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4417,7 +4473,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4441,7 +4497,7 @@
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -4452,10 +4508,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4484,7 +4540,7 @@
         <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>142</v>
@@ -4525,10 +4581,10 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>20</v>
@@ -4537,7 +4593,7 @@
         <v>199</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4561,7 +4617,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4572,10 +4628,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4601,23 +4657,23 @@
         <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>20</v>
@@ -4659,7 +4715,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4680,10 +4736,10 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -4694,10 +4750,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4720,16 +4776,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4779,7 +4835,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -4800,10 +4856,10 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -4814,10 +4870,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4843,21 +4899,21 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>20</v>
@@ -4899,7 +4955,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -4920,10 +4976,10 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -4934,10 +4990,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4960,17 +5016,17 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5019,7 +5075,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5040,10 +5096,10 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5054,10 +5110,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5080,19 +5136,19 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5141,7 +5197,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5162,10 +5218,10 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5176,10 +5232,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5202,19 +5258,19 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5263,7 +5319,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5284,10 +5340,10 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5298,14 +5354,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5321,22 +5377,22 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>194</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5361,13 +5417,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5385,7 +5441,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -5394,36 +5450,36 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>207</v>
+        <v>297</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>20</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5446,13 +5502,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5503,7 +5559,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5527,7 +5583,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5538,10 +5594,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5567,10 +5623,10 @@
         <v>139</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5609,10 +5665,10 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
@@ -5621,7 +5677,7 @@
         <v>199</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5656,10 +5712,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5679,22 +5735,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5743,7 +5799,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5752,7 +5808,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
@@ -5764,10 +5820,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>307</v>
+        <v>226</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>308</v>
+        <v>227</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -5778,10 +5834,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5804,19 +5860,19 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5865,7 +5921,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5886,10 +5942,10 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -5900,10 +5956,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5926,19 +5982,19 @@
         <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5987,7 +6043,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6002,19 +6058,19 @@
         <v>104</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>20</v>
@@ -6022,10 +6078,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6048,16 +6104,16 @@
         <v>93</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6107,7 +6163,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6128,13 +6184,13 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>326</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>20</v>
@@ -6689,7 +6745,7 @@
         <v>20</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y39" t="s" s="2">
         <v>374</v>
@@ -6811,7 +6867,7 @@
         <v>20</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y40" t="s" s="2">
         <v>386</v>
@@ -6844,7 +6900,7 @@
         <v>92</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>205</v>
+        <v>388</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>104</v>
@@ -6856,10 +6912,10 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>207</v>
+        <v>389</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
@@ -6870,14 +6926,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6899,16 +6955,16 @@
         <v>191</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6933,13 +6989,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6957,7 +7013,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6966,7 +7022,7 @@
         <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>104</v>
@@ -6975,27 +7031,27 @@
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>20</v>
+        <v>398</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>206</v>
+        <v>399</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>207</v>
+        <v>400</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7018,19 +7074,19 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -7079,7 +7135,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7100,10 +7156,10 @@
         <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7114,10 +7170,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7143,13 +7199,13 @@
         <v>191</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7175,13 +7231,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -7199,7 +7255,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7208,7 +7264,7 @@
         <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>104</v>
@@ -7217,27 +7273,27 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>206</v>
+        <v>417</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>207</v>
+        <v>418</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>20</v>
+        <v>419</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7263,16 +7319,16 @@
         <v>191</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7297,13 +7353,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7321,7 +7377,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7330,7 +7386,7 @@
         <v>92</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ44" t="s" s="2">
         <v>104</v>
@@ -7342,10 +7398,10 @@
         <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>206</v>
+        <v>427</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>207</v>
+        <v>428</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>20</v>
@@ -7356,10 +7412,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7382,16 +7438,16 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7441,7 +7497,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7459,27 +7515,27 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7502,16 +7558,16 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>430</v>
+        <v>442</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7561,7 +7617,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7579,27 +7635,27 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>434</v>
+        <v>446</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7622,19 +7678,19 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7683,7 +7739,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7695,7 +7751,7 @@
         <v>20</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>441</v>
+        <v>453</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>20</v>
@@ -7704,10 +7760,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7718,10 +7774,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7744,13 +7800,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7801,7 +7857,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7825,7 +7881,7 @@
         <v>20</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7836,10 +7892,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7868,7 +7924,7 @@
         <v>140</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>142</v>
@@ -7921,7 +7977,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7945,7 +8001,7 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -7956,14 +8012,14 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
@@ -7985,10 +8041,10 @@
         <v>139</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="N50" t="s" s="2">
         <v>142</v>
@@ -8043,7 +8099,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8078,10 +8134,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8104,13 +8160,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -8161,7 +8217,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8170,7 +8226,7 @@
         <v>92</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>104</v>
@@ -8182,10 +8238,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8196,10 +8252,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8222,13 +8278,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8279,7 +8335,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8288,7 +8344,7 @@
         <v>92</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>104</v>
@@ -8300,10 +8356,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8314,10 +8370,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8343,16 +8399,16 @@
         <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>463</v>
+        <v>475</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8380,10 +8436,10 @@
         <v>117</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>20</v>
@@ -8401,7 +8457,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8410,7 +8466,7 @@
         <v>92</v>
       </c>
       <c r="AI53" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ53" t="s" s="2">
         <v>104</v>
@@ -8419,13 +8475,13 @@
         <v>20</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>20</v>
+        <v>480</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>206</v>
+        <v>481</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>207</v>
+        <v>400</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8436,10 +8492,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8465,16 +8521,16 @@
         <v>191</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>469</v>
+        <v>483</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>470</v>
+        <v>484</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>471</v>
+        <v>485</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>20</v>
@@ -8499,13 +8555,13 @@
         <v>20</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>473</v>
+        <v>487</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>474</v>
+        <v>488</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>20</v>
@@ -8523,7 +8579,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8532,7 +8588,7 @@
         <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
@@ -8541,13 +8597,13 @@
         <v>20</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>20</v>
+        <v>480</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>206</v>
+        <v>481</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>207</v>
+        <v>400</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>20</v>
@@ -8558,10 +8614,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8584,17 +8640,17 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>20</v>
@@ -8643,7 +8699,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>475</v>
+        <v>489</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -8667,7 +8723,7 @@
         <v>20</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>20</v>
@@ -8678,10 +8734,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8704,13 +8760,13 @@
         <v>20</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8761,7 +8817,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8782,10 +8838,10 @@
         <v>20</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>456</v>
+        <v>468</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -8796,10 +8852,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8822,16 +8878,16 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8881,7 +8937,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -8902,10 +8958,10 @@
         <v>20</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>20</v>
@@ -8916,10 +8972,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8942,16 +8998,16 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9001,7 +9057,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9022,10 +9078,10 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
@@ -9036,10 +9092,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9062,19 +9118,19 @@
         <v>93</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -9123,7 +9179,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9135,7 +9191,7 @@
         <v>20</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>20</v>
@@ -9144,10 +9200,10 @@
         <v>20</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9158,10 +9214,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9184,13 +9240,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9241,7 +9297,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9265,7 +9321,7 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9276,10 +9332,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9308,7 +9364,7 @@
         <v>140</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>142</v>
@@ -9361,7 +9417,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9385,7 +9441,7 @@
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9396,14 +9452,14 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9425,10 +9481,10 @@
         <v>139</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>142</v>
@@ -9483,7 +9539,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9518,10 +9574,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9541,22 +9597,22 @@
         <v>20</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K63" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>510</v>
+        <v>524</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>20</v>
@@ -9581,13 +9637,13 @@
         <v>20</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>20</v>
@@ -9605,7 +9661,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>92</v>
@@ -9614,7 +9670,7 @@
         <v>92</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>104</v>
@@ -9623,16 +9679,16 @@
         <v>20</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>20</v>
+        <v>528</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>207</v>
+        <v>297</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>20</v>
@@ -9640,10 +9696,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9669,16 +9725,16 @@
         <v>369</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>515</v>
+        <v>530</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>516</v>
+        <v>531</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>517</v>
+        <v>532</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>518</v>
+        <v>533</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9703,13 +9759,13 @@
         <v>20</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>519</v>
+        <v>534</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>520</v>
+        <v>535</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>20</v>
@@ -9727,7 +9783,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>514</v>
+        <v>529</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9736,7 +9792,7 @@
         <v>92</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>521</v>
+        <v>536</v>
       </c>
       <c r="AJ64" t="s" s="2">
         <v>104</v>
@@ -9745,7 +9801,7 @@
         <v>20</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>378</v>
@@ -9762,10 +9818,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9791,10 +9847,10 @@
         <v>191</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>524</v>
+        <v>539</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>525</v>
+        <v>540</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>384</v>
@@ -9825,10 +9881,10 @@
         <v>20</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>526</v>
+        <v>541</v>
       </c>
       <c r="Z65" t="s" s="2">
         <v>387</v>
@@ -9849,7 +9905,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>523</v>
+        <v>538</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9858,7 +9914,7 @@
         <v>92</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>205</v>
+        <v>542</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>104</v>
@@ -9870,10 +9926,10 @@
         <v>20</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>207</v>
+        <v>389</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>20</v>
@@ -9884,14 +9940,14 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
@@ -9913,16 +9969,16 @@
         <v>191</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>20</v>
@@ -9947,13 +10003,13 @@
         <v>20</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>529</v>
+        <v>545</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>20</v>
@@ -9971,7 +10027,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>527</v>
+        <v>543</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -9980,7 +10036,7 @@
         <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>104</v>
@@ -9989,27 +10045,27 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>20</v>
+        <v>398</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>206</v>
+        <v>399</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>207</v>
+        <v>400</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10035,16 +10091,16 @@
         <v>82</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>531</v>
+        <v>547</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>532</v>
+        <v>548</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>20</v>
@@ -10093,7 +10149,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>530</v>
+        <v>546</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10114,10 +10170,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
+++ b/docs/StructureDefinition-LTCObservationVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
